--- a/docs/web-copy-master.xlsx
+++ b/docs/web-copy-master.xlsx
@@ -43,7 +43,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +60,9 @@
     <font>
       <name val="Meiryo"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
     </font>
   </fonts>
   <fills count="7">
@@ -121,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +147,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6145,7 +6149,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Moments Share：「やってよかった」と思える瞬間を、共につくろう。／ 最後まで向き合い、喜びを分かち合おう。</t>
+          <t>Moments Share：「やりきってよかった」と思える瞬間を、共につくろう。／ 最後まで向き合い、喜びを分かち合おう。</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -12275,7 +12279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12369,6 +12373,38 @@
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Moments Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>ABOUT-VALUES-06</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>「やってよかった」と思える瞬間を、共につくろう。</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>「やりきってよかった」と思える瞬間を、共につくろう。</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>表現調整（『やって』→『やりきって』）</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Moments Share</t>
         </is>
@@ -15474,7 +15510,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Moments Share：「やってよかった」と思える瞬間を、共につくろう。／ 最後まで向き合い、喜びを分かち合おう。</t>
+          <t>Moments Share：「やりきってよかった」と思える瞬間を、共につくろう。／ 最後まで向き合い、喜びを分かち合おう。</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">

--- a/docs/web-copy-master.xlsx
+++ b/docs/web-copy-master.xlsx
@@ -6171,7 +6171,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-07</t>
+          <t>ABOUT-VALUES-09</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Legacy：100年後に、誇れる選択を。</t>
+          <t>Self Driven：自分ごとで動こう。</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -6213,7 +6213,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-08</t>
+          <t>ABOUT-VALUES-10</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Purpose：目的から、考えよう。</t>
+          <t>Challenge：まず、やってみよう。</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-09</t>
+          <t>ABOUT-VALUES-12</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Self Driven：自分ごとで動こう。</t>
+          <t>Better Everyday：昨日より、少しずつ良くしよう。</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -6297,7 +6297,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-10</t>
+          <t>ABOUT-VALUES-07</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Challenge：まず、やってみよう。</t>
+          <t>Legacy：100年後に、誇れる選択を。</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -6339,7 +6339,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-11</t>
+          <t>ABOUT-VALUES-08</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Co-Create：違いを力に、共に創ろう。</t>
+          <t>Purpose：目的から、考えよう。</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -6381,7 +6381,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-12</t>
+          <t>ABOUT-VALUES-11</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Better Everyday：昨日より、少しずつ良くしよう。</t>
+          <t>Co-Create：違いを力に、共に創ろう。</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -12279,7 +12279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12405,6 +12405,38 @@
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Moments Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>ABOUT-VALUES(判断基準)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Legacy→Purpose→Self Driven→Challenge→Co-Create→Better Everyday→Build Systems</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Self Driven→Challenge→Better Everyday→Legacy→Purpose→Co-Create→Build Systems</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>7つの判断基準の表示順を変更</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Moments Share</t>
         </is>
@@ -15532,7 +15564,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-07</t>
+          <t>ABOUT-VALUES-09</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -15547,7 +15579,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Legacy：100年後に、誇れる選択を。</t>
+          <t>Self Driven：自分ごとで動こう。</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -15569,7 +15601,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-08</t>
+          <t>ABOUT-VALUES-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -15584,7 +15616,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Purpose：目的から、考えよう。</t>
+          <t>Challenge：まず、やってみよう。</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -15606,7 +15638,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-09</t>
+          <t>ABOUT-VALUES-12</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -15621,7 +15653,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Self Driven：自分ごとで動こう。</t>
+          <t>Better Everyday：昨日より、少しずつ良くしよう。</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -15643,7 +15675,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-10</t>
+          <t>ABOUT-VALUES-07</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -15658,7 +15690,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Challenge：まず、やってみよう。</t>
+          <t>Legacy：100年後に、誇れる選択を。</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -15680,7 +15712,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-11</t>
+          <t>ABOUT-VALUES-08</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -15695,7 +15727,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Co-Create：違いを力に、共に創ろう。</t>
+          <t>Purpose：目的から、考えよう。</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -15717,7 +15749,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ABOUT-VALUES-12</t>
+          <t>ABOUT-VALUES-11</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -15732,7 +15764,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Better Everyday：昨日より、少しずつ良くしよう。</t>
+          <t>Co-Create：違いを力に、共に創ろう。</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">

--- a/docs/web-copy-master.xlsx
+++ b/docs/web-copy-master.xlsx
@@ -65,7 +65,7 @@
       <name val="Meiryo"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +97,11 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -148,6 +153,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2165,7 +2182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H234"/>
+  <dimension ref="A1:H236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5984,14 +6001,14 @@
           <t>存在意義を、日々の選択に。</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>検討中</t>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>廃止</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>VALUES再構成で見出し廃止（核コピーに置換）</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -12001,6 +12018,90 @@
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="10" t="inlineStr">
+        <is>
+          <t>ABOUT-VALUES-CORE-001</t>
+        </is>
+      </c>
+      <c r="B235" s="10" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="C235" s="10" t="inlineStr">
+        <is>
+          <t>VALUES</t>
+        </is>
+      </c>
+      <c r="D235" s="10" t="inlineStr">
+        <is>
+          <t>核コピー</t>
+        </is>
+      </c>
+      <c r="E235" s="11" t="inlineStr">
+        <is>
+          <t>一歩ずつ、できるまで続けるだけ。</t>
+        </is>
+      </c>
+      <c r="F235" s="12" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="G235" s="11" t="inlineStr">
+        <is>
+          <t>Valueの核（行動基準×判断基準の起点）</t>
+        </is>
+      </c>
+      <c r="H235" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="inlineStr">
+        <is>
+          <t>ABOUT-VALUES-BRIDGE-001</t>
+        </is>
+      </c>
+      <c r="B236" s="10" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="C236" s="10" t="inlineStr">
+        <is>
+          <t>VALUES</t>
+        </is>
+      </c>
+      <c r="D236" s="10" t="inlineStr">
+        <is>
+          <t>ブリッジ</t>
+        </is>
+      </c>
+      <c r="E236" s="11" t="inlineStr">
+        <is>
+          <t>その一歩を、3つの行動基準と7つの判断基準で支える。</t>
+        </is>
+      </c>
+      <c r="F236" s="12" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="G236" s="11" t="inlineStr">
+        <is>
+          <t>核と基準を繋ぐ橋渡し文</t>
+        </is>
+      </c>
+      <c r="H236" s="10" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -12279,7 +12380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12437,6 +12538,38 @@
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Moments Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>ABOUT-VALUES-CORE-001</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>（新規）</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>一歩ずつ、できるまで続けるだけ。</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Valueの核を新設し、行動基準×判断基準を連結する構成に再編</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Moments Share</t>
         </is>
@@ -14587,7 +14720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15397,14 +15530,14 @@
           <t>存在意義を、日々の選択に。</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>検討中</t>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>廃止</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>VALUES再構成で見出し廃止（核コピーに置換）</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -16111,6 +16244,80 @@
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>ABOUT-VALUES-CORE-001</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>VALUES</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>核コピー</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>一歩ずつ、できるまで続けるだけ。</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Valueの核（行動基準×判断基準の起点）</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>ABOUT-VALUES-BRIDGE-001</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>VALUES</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>ブリッジ</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>その一歩を、3つの行動基準と7つの判断基準で支える。</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>核と基準を繋ぐ橋渡し文</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>

--- a/docs/web-copy-master.xlsx
+++ b/docs/web-copy-master.xlsx
@@ -34,7 +34,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'地域プロデュース'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'WEB文言マスター'!$A$1:$H$234</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'ブランド言語'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'変更履歴'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'変更履歴'!$A$1:$F$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -745,7 +745,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>カタチにしてきたこと。／ 業務を、余白に変えた事例。</t>
+          <t>ひとつずつ、形に。／ 業務を、余白に変えた事例。</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>「人手不足を、多様な働き方へ。」採用前に仕事を整理し外部で支える提案。</t>
+          <t>「人手不足に、社外の力を。」採用前に仕事を整理し外部で支える提案。</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>人手不足を、多様な働き方へ。／ その仕事、本当に採用が必要ですか？</t>
+          <t>人手不足に、社外の力を。／ その仕事、本当に採用が必要ですか？</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>「地域課題を、挑戦のきっかけへ。」人・企業・地域をつなぎ挑戦の場をつくる。</t>
+          <t>「想いを、挑戦へ。」人・企業・地域をつなぎ挑戦の場をつくる。</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>地域課題を、挑戦のきっかけへ。／ 2040年までに、西尾に240の事業を。</t>
+          <t>想いを、挑戦へ。／ 2040年までに、西尾に240の事業を。</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>地域課題を、挑戦のきっかけへ。</t>
+          <t>想いを、挑戦へ。</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>正本。★TOP事業・service-produce H1は一致だが、EcosystemCircle.tsx（PC/モバイル）は「…きっかけに。」で不一致。残置Ecosystem.tsxも「…に。」。要修正</t>
+          <t>正本。TOP事業・service-produce H1と一致。2026-08-26に「地域課題を、挑戦のきっかけへ。」から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>地域課題を、挑戦のきっかけへ。</t>
+          <t>想いを、挑戦へ。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>service-produce h1。SERVICE-REGION-001と一致</t>
+          <t>service-produce h1。SERVICE-REGION-001と一致。2026-08-26更新</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>人手不足を、多様な働き方へ。</t>
+          <t>人手不足に、社外の力を。</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>正本。service-bpo H1・TOP事業・EcosystemCircleと一致</t>
+          <t>正本。service-bpo H1・TOP事業・EcosystemCircleと一致。2026-08-26に「人手不足を、多様な働き方へ。」から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>地域課題を、挑戦のきっかけへ。</t>
+          <t>想いを、挑戦へ。</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>正本。★TOP事業・service-produce H1は一致だが、EcosystemCircle.tsx（PC/モバイル）は「…きっかけに。」で不一致。残置Ecosystem.tsxも「…に。」。要修正</t>
+          <t>正本。TOP事業・service-produce H1と一致。2026-08-26に「地域課題を、挑戦のきっかけへ。」から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>地域に、240の事業を共創する。</t>
+          <t>西尾から、240の事業を。</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>正本。VisionNishio.tsx（地域に、／240／の事業を共創する。）と一致</t>
+          <t>正本。VisionNishio.tsx（西尾から、／240／の事業を。）と一致。2026-08-26に「地域に、240の事業を共創する。」から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>人手不足を、多様な働き方へ。</t>
+          <t>人手不足に、社外の力を。</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>EcosystemCircle BPOキャッチ。SERVICE-BPO-001と一致</t>
+          <t>EcosystemCircle BPOキャッチ。SERVICE-BPO-001と一致。2026-08-26更新</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -3898,22 +3898,22 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>地域課題を、挑戦のきっかけに。</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>想いを、挑戦へ。</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>EcosystemCircle 地域キャッチ。★確定SERVICE-REGION-001「…きっかけへ。」と不一致（現行は「…に。」）。要修正</t>
+          <t>EcosystemCircle 地域キャッチ。SERVICE-REGION-001と一致。2026-08-26更新によりTOP-BUSINESS-04表記と整合（旧不一致を解消）</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>業務を整理し、AI・RPA・自動化を使って、人がやらなくてもいい仕事を減らします。</t>
+          <t>AI導入・システム開発・研修を通じて企業の業務改善に伴走し、新しいことに取り組める時間をつくります。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>page.tsx DX本文</t>
+          <t>page.tsx DX本文。2026-08-26に公開版仕上げの実装へ同期</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>企業に必要な仕事を整理し、外部のチームと一緒に支えます。</t>
+          <t>営業・事務・CS等を受託し、社外パートナーとチームを組んで企業を支えます。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>page.tsx BPO本文</t>
+          <t>page.tsx BPO本文。2026-08-26に公開版仕上げの実装へ同期</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>地域課題を、挑戦のきっかけへ。</t>
+          <t>想いを、挑戦へ。</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>page.tsx 地域タイトル。SERVICE-REGION-001と一致</t>
+          <t>正本。page.tsx 地域タイトル。SERVICE-REGION-001と一致。2026-08-26更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>人・企業・地域をつなぎ、新しい挑戦が生まれる場をつくります。</t>
+          <t>個の「やりたい」と地域の「課題」をつなぎ、地域内外の人や企業とともに新しい仕事や事業をつくります。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>page.tsx 地域本文</t>
+          <t>page.tsx 地域本文。2026-08-26に公開版仕上げの実装へ同期</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>OUR VISION ／ 2040年 Vision</t>
+          <t>OUR VISION ／ 2040 GOAL</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>VisionNishio.tsx</t>
+          <t>VisionNishio.tsx ラベル。2026-08-26更新（旧「2040年 Vision」表記を実装に合わせ修正）</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>挑戦と共創の循環が、地域の未来を動かす。</t>
+          <t>西尾から、240の事業を。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>VisionNishio.tsx</t>
+          <t>VisionNishio.tsx 見出し。GOAL-2040-001と同一。2026-08-26更新</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>地域の可能性を信じ、挑戦がめぐり続けるまちへ。</t>
+          <t>挑戦が当たり前になり、地域内外の人や企業とともに、事業を共創し続ける。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>VisionNishio.tsx</t>
+          <t>VisionNishio.tsx 補足文。2026-08-26更新</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>BPO：BPO（業務代行）／ 人手不足を、多様な働き方へ。／ 採用して人を増やす前に、仕事を外に出すという選択肢を。カスタマーサクセス・営業支援・SNS・経理事務。必要な仕事を、必要な分だけ支える。</t>
+          <t>BPO：BPO（業務代行）／ 人手不足に、社外の力を。／ 採用して人を増やす前に、仕事を外に出すという選択肢を。カスタマーサクセス・営業支援・SNS・経理事務。必要な仕事を、必要な分だけ支える。</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>about businesses</t>
+          <t>about businesses。2026-08-26にリード「人手不足を、多様な働き方へ。」→「人手不足に、社外の力を。」へ同期</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>カタチにしてきたこと。</t>
+          <t>ひとつずつ、形に。</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>works h1</t>
+          <t>works h1。2026-08-26に「カタチにしてきたこと。」から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>7件：DX・業務効率化の支援 ／ 3社：BPO支援 ／ 5名：外部パートナー ／ 4件：地域プロジェクト</t>
+          <t>事業 4／240（KPI） ／ DX：AI導入支援 1社・AI研修 2社・システム開発 2件実施中・効率化フロー 7件 ／ BPO：業務代行支援 3社・CS、SNS運用、事務 ／ 地域プロデュース：挑戦プロジェクト 4件 ／ PARTNERS：ともに働くパートナー 5名</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>works stats（TOPと共通）</t>
+          <t>works kpi(now4/goal240/label事業)＋カテゴリ別実績（現行実装）。2026-08-26に旧stats表記から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>人手不足を、多様な働き方へ。</t>
+          <t>人手不足に、社外の力を。</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>service-bpo h1。SERVICE-BPO-001と一致</t>
+          <t>service-bpo h1。SERVICE-BPO-001と一致。2026-08-26更新</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>地域課題を、挑戦のきっかけへ。</t>
+          <t>想いを、挑戦へ。</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>service-produce h1。SERVICE-REGION-001と一致</t>
+          <t>service-produce h1。SERVICE-REGION-001と一致。2026-08-26更新</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>地域に、240の事業を共創する。</t>
+          <t>西尾から、240の事業を。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12575,8 +12575,224 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>TOP-BUSINESS-02/03/05</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>page.tsx BUSINESSカードの旧本文</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>AI導入・システム開発・研修を通じて…／営業・事務・CS等を受託し…／個の「やりたい」と地域の「課題」をつなぎ…</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>公開版仕上げの確定コピーに同期（BUSINESS 3事業カードの本文）</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>SERVICE-BPO-001 / TOP-ECOSYSTEM-05 / BPO-HERO-02 / ABOUT-HOW-04 / TOP-BUSINESS-04</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>人手不足を、多様な働き方へ。</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>人手不足に、社外の力を。</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>BPOのリードを公開版仕上げの確定コピーに同期</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>SERVICE-REGION-001 / TOP-ECOSYSTEM-06 / PRODUCE-HERO-02 / TOP-BUSINESS-04</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>地域課題を、挑戦のきっかけへ。／地域課題を、挑戦のきっかけに。</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>想いを、挑戦へ。</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>地域プロデュースのリードを公開版仕上げの確定コピーに同期。TOP-ECOSYSTEM-06の要確認（表記不一致）も解消</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>GOAL-2040-001 / TOP-VISION-01/02/03 / ブランド言語(2040 GOAL)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>地域に、240の事業を共創する。／OUR VISION ／ 2040年 Vision　他</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>西尾から、240の事業を。／OUR VISION ／ 2040 GOAL／挑戦が当たり前になり、地域内外の人や企業とともに、事業を共創し続ける。</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2040 GOAL（VisionNishio.tsx）を公開版仕上げの確定コピーに同期</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>WORKS-HERO-02 / WORKS-STATS-01</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>カタチにしてきたこと。／7件：DX・業務効率化の支援 ／ 3社：BPO支援 ／ 5名：外部パートナー ／ 4件：地域プロジェクト</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>ひとつずつ、形に。／事業4／240（KPI）＋DX・BPO・地域プロデュース・PARTNERSのカテゴリ別実績</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>WORKS（works/page.tsx）のH1・数字セクションを公開版仕上げの確定コピーに同期</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>ABOUT-VALUES-CORE-001 / ABOUT-VALUES-BRIDGE-001</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>（変更なし・整合確認のみ）</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>VALUES核「一歩ずつ、できるまで続けるだけ。」とブリッジ文は既にabout/page.tsxと一致していることを確認</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ページ構成（BPO/地域プロデュース/Works） / ブランド言語（2040 GOAL）</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>埋め込みリード・目標コピーを上記に合わせて更新</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>サマリー系シート内の埋め込み旧コピーを実装同期に合わせて更新</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12765,7 +12981,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>地域に、240の事業を共創する。</t>
+          <t>西尾から、240の事業を。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12775,12 +12991,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>正本。VisionNishio.tsx（地域に、／240／の事業を共創する。）と一致</t>
+          <t>正本。VisionNishio.tsx（西尾から、／240／の事業を。）と一致。2026-08-26に「地域に、240の事業を共創する。」から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13795,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>人手不足を、多様な働き方へ。</t>
+          <t>人手不足に、社外の力を。</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13589,12 +13805,12 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>EcosystemCircle BPOキャッチ。SERVICE-BPO-001と一致</t>
+          <t>EcosystemCircle BPOキャッチ。SERVICE-BPO-001と一致。2026-08-26更新</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -13616,22 +13832,22 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>地域課題を、挑戦のきっかけに。</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>想いを、挑戦へ。</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>EcosystemCircle 地域キャッチ。★確定SERVICE-REGION-001「…きっかけへ。」と不一致（現行は「…に。」）。要修正</t>
+          <t>EcosystemCircle 地域キャッチ。SERVICE-REGION-001と一致。2026-08-26更新によりTOP-BUSINESS-04表記と整合（旧不一致を解消）</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -13727,7 +13943,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>業務を整理し、AI・RPA・自動化を使って、人がやらなくてもいい仕事を減らします。</t>
+          <t>AI導入・システム開発・研修を通じて企業の業務改善に伴走し、新しいことに取り組める時間をつくります。</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -13737,12 +13953,12 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>page.tsx DX本文</t>
+          <t>page.tsx DX本文。2026-08-26に公開版仕上げの実装へ同期</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -13764,7 +13980,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>企業に必要な仕事を整理し、外部のチームと一緒に支えます。</t>
+          <t>営業・事務・CS等を受託し、社外パートナーとチームを組んで企業を支えます。</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -13774,12 +13990,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>page.tsx BPO本文</t>
+          <t>page.tsx BPO本文。2026-08-26に公開版仕上げの実装へ同期</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -13801,7 +14017,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>地域課題を、挑戦のきっかけへ。</t>
+          <t>想いを、挑戦へ。</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13811,12 +14027,12 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>page.tsx 地域タイトル。SERVICE-REGION-001と一致</t>
+          <t>正本。page.tsx 地域タイトル。SERVICE-REGION-001と一致。2026-08-26更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -13838,7 +14054,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>人・企業・地域をつなぎ、新しい挑戦が生まれる場をつくります。</t>
+          <t>個の「やりたい」と地域の「課題」をつなぎ、地域内外の人や企業とともに新しい仕事や事業をつくります。</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -13848,12 +14064,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>page.tsx 地域本文</t>
+          <t>page.tsx 地域本文。2026-08-26に公開版仕上げの実装へ同期</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -14504,7 +14720,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>OUR VISION ／ 2040年 Vision</t>
+          <t>OUR VISION ／ 2040 GOAL</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -14514,12 +14730,12 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>VisionNishio.tsx</t>
+          <t>VisionNishio.tsx ラベル。2026-08-26更新（旧「2040年 Vision」表記を実装に合わせ修正）</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14757,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>挑戦と共創の循環が、地域の未来を動かす。</t>
+          <t>西尾から、240の事業を。</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -14551,12 +14767,12 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>VisionNishio.tsx</t>
+          <t>VisionNishio.tsx 見出し。GOAL-2040-001と同一。2026-08-26更新</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14794,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>地域の可能性を信じ、挑戦がめぐり続けるまちへ。</t>
+          <t>挑戦が当たり前になり、地域内外の人や企業とともに、事業を共創し続ける。</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -14588,12 +14804,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>VisionNishio.tsx</t>
+          <t>VisionNishio.tsx 補足文。2026-08-26更新</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15336,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>BPO：BPO（業務代行）／ 人手不足を、多様な働き方へ。／ 採用して人を増やす前に、仕事を外に出すという選択肢を。カスタマーサクセス・営業支援・SNS・経理事務。必要な仕事を、必要な分だけ支える。</t>
+          <t>BPO：BPO（業務代行）／ 人手不足に、社外の力を。／ 採用して人を増やす前に、仕事を外に出すという選択肢を。カスタマーサクセス・営業支援・SNS・経理事務。必要な仕事を、必要な分だけ支える。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -15130,12 +15346,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>about businesses</t>
+          <t>about businesses。2026-08-26にリード「人手不足を、多様な働き方へ。」→「人手不足に、社外の力を。」へ同期</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17456,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>カタチにしてきたこと。</t>
+          <t>ひとつずつ、形に。</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -17250,12 +17466,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>works h1</t>
+          <t>works h1。2026-08-26に「カタチにしてきたこと。」から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -17314,7 +17530,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>7件：DX・業務効率化の支援 ／ 3社：BPO支援 ／ 5名：外部パートナー ／ 4件：地域プロジェクト</t>
+          <t>事業 4／240（KPI） ／ DX：AI導入支援 1社・AI研修 2社・システム開発 2件実施中・効率化フロー 7件 ／ BPO：業務代行支援 3社・CS、SNS運用、事務 ／ 地域プロデュース：挑戦プロジェクト 4件 ／ PARTNERS：ともに働くパートナー 5名</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -17324,12 +17540,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>works stats（TOPと共通）</t>
+          <t>works kpi(now4/goal240/label事業)＋カテゴリ別実績（現行実装）。2026-08-26に旧stats表記から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -19704,7 +19920,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>人手不足を、多様な働き方へ。</t>
+          <t>人手不足に、社外の力を。</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -19714,12 +19930,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>正本。service-bpo H1・TOP事業・EcosystemCircleと一致</t>
+          <t>正本。service-bpo H1・TOP事業・EcosystemCircleと一致。2026-08-26に「人手不足を、多様な働き方へ。」から更新（公開版仕上げ）</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -19889,7 +20105,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>人手不足を、多様な働き方へ。</t>
+          <t>人手不足に、社外の力を。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -19899,12 +20115,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>service-bpo h1。SERVICE-BPO-001と一致</t>
+          <t>service-bpo h1。SERVICE-BPO-001と一致。2026-08-26更新</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
